--- a/framework/assets/plantillas/Plantilla_nomenclaturas_y_UTM_casa_apuestas.xlsx
+++ b/framework/assets/plantillas/Plantilla_nomenclaturas_y_UTM_casa_apuestas.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'01_Plataformas'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'03_UTMs'!$1:$17</definedName>
   </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -193,7 +193,7 @@
     <t>✓</t>
   </si>
   <si>
-    <t>Separador principal: | (barra vertical).</t>
+    <t>Separador principal: _ (guion bajo).</t>
   </si>
   <si>
     <t>El número de orden se usa solo en objetos de plataforma.</t>
@@ -313,7 +313,7 @@
     <t>Responsable</t>
   </si>
   <si>
-    <t>01 · Adquisición | Bono de bienvenida | CO | Sep 2026</t>
+    <t>01_ADQUISICIÓN_Bono de bienvenida_CO_Sep 2026</t>
   </si>
   <si>
     <t>Prospección</t>
@@ -328,13 +328,13 @@
     <t>Equipo Paid Media</t>
   </si>
   <si>
-    <t>02 · Conversión | Apuestas deportivas | CO | Sep 2026</t>
+    <t>02_CONVERSIÓN_Apuestas deportivas_CO_Sep 2026</t>
   </si>
   <si>
     <t>Palabras clave</t>
   </si>
   <si>
-    <t>03 · Retención | Recarga y vuelve a jugar | CO | Q4 2026</t>
+    <t>03_RETENCIÓN_Recarga y vuelve a jugar_CO_Q4 2026</t>
   </si>
   <si>
     <t>CRM</t>
@@ -346,7 +346,7 @@
     <t>30 días</t>
   </si>
   <si>
-    <t>04 · Consideración | Pronósticos deportivos | CO | Sep 2026</t>
+    <t>04_CONSIDERACIÓN_Pronósticos deportivos_CO_Sep 2026</t>
   </si>
   <si>
     <t>Remarketing</t>
@@ -373,7 +373,7 @@
     <t>Versión</t>
   </si>
   <si>
-    <t>01 · Prospección | Fútbol | Amplia</t>
+    <t>01_PROSPECCIÓN_Fútbol_Amplia</t>
   </si>
   <si>
     <t>Video</t>
@@ -385,7 +385,7 @@
     <t>V01</t>
   </si>
   <si>
-    <t>02 · Prospección | Apuestas deportivas | Palabras clave</t>
+    <t>02_PROSPECCIÓN_Apuestas deportivas_Palabras clave</t>
   </si>
   <si>
     <t>Responsive Search Ad</t>
@@ -397,7 +397,7 @@
     <t>Juega ahora</t>
   </si>
   <si>
-    <t>03 · CRM | Jugadores inactivos | 30 días</t>
+    <t>03_CRM_Jugadores inactivos_30 días</t>
   </si>
   <si>
     <t>Estático</t>
@@ -409,7 +409,7 @@
     <t>Recarga</t>
   </si>
   <si>
-    <t>04 · Remarketing | Video viewers | 30 días</t>
+    <t>04_REMARKETING_Video viewers_30 días</t>
   </si>
   <si>
     <t>Pronóstico del partido</t>
@@ -454,7 +454,7 @@
     <t>Advantage</t>
   </si>
   <si>
-    <t>Prospección | Deportes | Advantage</t>
+    <t>PROSPECCIÓN_Deportes_Advantage</t>
   </si>
   <si>
     <t>Activo</t>
@@ -466,13 +466,13 @@
     <t>IG</t>
   </si>
   <si>
-    <t>Remarketing | IG · Interacciones | 30 días</t>
+    <t>REMARKETING_IG Interacciones_30 días</t>
   </si>
   <si>
     <t>Recaptura</t>
   </si>
   <si>
-    <t>CRM | Jugadores inactivos | CRM</t>
+    <t>CRM_Jugadores inactivos_CRM</t>
   </si>
   <si>
     <t>Reactivación</t>
@@ -493,7 +493,7 @@
     <t>2%</t>
   </si>
   <si>
-    <t>Similar | Depositantes | 2%</t>
+    <t>SIMILAR_Depositantes_2%</t>
   </si>
   <si>
     <t>Expansión</t>
@@ -529,10 +529,10 @@
     <t>Carpeta cliente</t>
   </si>
   <si>
-    <t>[Cliente] | [Agencia] | [Vigencia]</t>
-  </si>
-  <si>
-    <t>Casa apuestas | Adcom | Activo</t>
+    <t>[CLIENTE]_[AGENCIA]_[ESTADO]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_ADCOM_ACTIVO</t>
   </si>
   <si>
     <t>Una carpeta raíz por cliente.</t>
@@ -559,10 +559,10 @@
     <t>No repetir el cliente si la ruta lo hereda.</t>
   </si>
   <si>
-    <t>[Cliente] | [Periodo]</t>
-  </si>
-  <si>
-    <t>Casa apuestas | 2026-09</t>
+    <t>[CLIENTE]_[AAAA-MM]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_2026-09</t>
   </si>
   <si>
     <t>Usar AAAA-MM.</t>
@@ -571,10 +571,10 @@
     <t>Documento estratégico</t>
   </si>
   <si>
-    <t>[Tipo] | [Tema] | [Periodo]</t>
-  </si>
-  <si>
-    <t>Estrategia | Adquisición de jugadores | Q4 2026</t>
+    <t>[CLIENTE]_[TIPO]_[Tema y periodo]_[Fecha]_[Versión]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_ESTRATEGIA_Adquisición de jugadores Q4 2026_10-09-26_V01</t>
   </si>
   <si>
     <t>Usar Mes AAAA o Q# AAAA.</t>
@@ -583,10 +583,10 @@
     <t>Flow</t>
   </si>
   <si>
-    <t>Flow | [Cliente] | [Nota] | [Periodo]</t>
-  </si>
-  <si>
-    <t>Flow | Casa apuestas | Sportsbook | Sep 2026</t>
+    <t>[CLIENTE]_FLOW_[Nota y periodo]_[Fecha]_[Versión]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_FLOW_Sportsbook Sep 2026_10-09-26_V01</t>
   </si>
   <si>
     <t>Incluir una nota solo si diferencia el escenario.</t>
@@ -595,10 +595,10 @@
     <t>Ruta estratégica</t>
   </si>
   <si>
-    <t>Ruta | [Cliente] | [Nota] | [Periodo]</t>
-  </si>
-  <si>
-    <t>Ruta | Casa apuestas | Bono de bienvenida | Sep 2026</t>
+    <t>[CLIENTE]_RUTA_[Nota y periodo]_[Fecha]_[Versión]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_RUTA_Bono de bienvenida Sep 2026_10-09-26_V01</t>
   </si>
   <si>
     <t>Agrupa campañas con intención común.</t>
@@ -607,10 +607,10 @@
     <t>Bitácora</t>
   </si>
   <si>
-    <t>Bitácora | [Cliente] | [DD-MM]</t>
-  </si>
-  <si>
-    <t>Bitácora | Casa apuestas | 04-09</t>
+    <t>[CLIENTE]_BITÁCORA_[Periodo]_[Fecha]_[Versión]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_BITÁCORA_Septiembre 2026_04-09-26_V01</t>
   </si>
   <si>
     <t>Usar DD-MM para seguimiento diario.</t>
@@ -619,10 +619,10 @@
     <t>Informe</t>
   </si>
   <si>
-    <t>Informe | [Tema] | [DD-MM]</t>
-  </si>
-  <si>
-    <t>Informe | Rendimiento sportsbook | 04-09</t>
+    <t>[CLIENTE]_INFORME_[Tema]_[Fecha]_[Versión]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_INFORME_Rendimiento sportsbook_04-09-26_V01</t>
   </si>
   <si>
     <t>El tema debe poder entenderse sin abrirlo.</t>
@@ -631,10 +631,10 @@
     <t>Implementación</t>
   </si>
   <si>
-    <t>Implementación | [Cliente] | [Periodo]</t>
-  </si>
-  <si>
-    <t>Implementación | Casa apuestas | 2026-09</t>
+    <t>[CLIENTE]_IMPLEMENTACIÓN_[Periodo]_[Fecha]_[Versión]</t>
+  </si>
+  <si>
+    <t>CASAAPUESTAS_IMPLEMENTACIÓN_2026-09_10-09-26_V01</t>
   </si>
   <si>
     <t>2. Metadatos de documentos</t>
@@ -709,7 +709,7 @@
     <t>3. Reglas de conversión</t>
   </si>
   <si>
-    <t>Usar | como separador principal; reemplazar guiones bajos heredados.</t>
+    <t>Usar _ como separador principal; reemplazar pipes y puntos medios heredados.</t>
   </si>
   <si>
     <t>No incluir el número de orden en carpetas ni documentos.</t>
@@ -2313,8 +2313,7 @@
         <v>56</v>
       </c>
       <c r="H9" s="6" t="str">
-        <f>IF(COUNTA(A9:G9)=0,"",TEXT(A9,"00")&amp;" · "&amp;D9&amp;" | "&amp;E9&amp;" | "&amp;F9&amp;" | "&amp;G9)</f>
-        <v>01 · Adquisición | Bono de bienvenida | CO | Sep 2026</v>
+        <f>IF(COUNTA(A9:G9)=0,"",TEXT(A9,"00")&amp;"_"&amp;UPPER(D9)&amp;"_"&amp;E9&amp;"_"&amp;UPPER(F9)&amp;"_"&amp;G9)</f>
       </c>
     </row>
     <row r="10" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2340,8 +2339,7 @@
         <v>56</v>
       </c>
       <c r="H10" s="6" t="str">
-        <f>IF(COUNTA(A10:G10)=0,"",TEXT(A10,"00")&amp;" · "&amp;D10&amp;" | "&amp;E10&amp;" | "&amp;F10&amp;" | "&amp;G10)</f>
-        <v>02 · Conversión | Apuestas deportivas | CO | Sep 2026</v>
+        <f>IF(COUNTA(A10:G10)=0,"",TEXT(A10,"00")&amp;"_"&amp;UPPER(D10)&amp;"_"&amp;E10&amp;"_"&amp;UPPER(F10)&amp;"_"&amp;G10)</f>
       </c>
     </row>
     <row r="11" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2367,8 +2365,7 @@
         <v>62</v>
       </c>
       <c r="H11" s="6" t="str">
-        <f>IF(COUNTA(A11:G11)=0,"",TEXT(A11,"00")&amp;" · "&amp;D11&amp;" | "&amp;E11&amp;" | "&amp;F11&amp;" | "&amp;G11)</f>
-        <v>03 · Retención | Recarga y vuelve a jugar | CO | Q4 2026</v>
+        <f>IF(COUNTA(A11:G11)=0,"",TEXT(A11,"00")&amp;"_"&amp;UPPER(D11)&amp;"_"&amp;E11&amp;"_"&amp;UPPER(F11)&amp;"_"&amp;G11)</f>
       </c>
     </row>
     <row r="12" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2394,8 +2391,7 @@
         <v>56</v>
       </c>
       <c r="H12" s="6" t="str">
-        <f>IF(COUNTA(A12:G12)=0,"",TEXT(A12,"00")&amp;" · "&amp;D12&amp;" | "&amp;E12&amp;" | "&amp;F12&amp;" | "&amp;G12)</f>
-        <v>04 · Consideración | Pronósticos deportivos | CO | Sep 2026</v>
+        <f>IF(COUNTA(A12:G12)=0,"",TEXT(A12,"00")&amp;"_"&amp;UPPER(D12)&amp;"_"&amp;E12&amp;"_"&amp;UPPER(F12)&amp;"_"&amp;G12)</f>
       </c>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2407,7 +2403,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="6" t="str">
-        <f>IF(COUNTA(A13:G13)=0,"",TEXT(A13,"00")&amp;" · "&amp;D13&amp;" | "&amp;E13&amp;" | "&amp;F13&amp;" | "&amp;G13)</f>
+        <f>IF(COUNTA(A13:G13)=0,"",TEXT(A13,"00")&amp;"_"&amp;UPPER(D13)&amp;"_"&amp;E13&amp;"_"&amp;UPPER(F13)&amp;"_"&amp;G13)</f>
         <v/>
       </c>
     </row>
@@ -2482,8 +2478,7 @@
         <v>76</v>
       </c>
       <c r="H17" s="6" t="str">
-        <f>IF(COUNTA(A17:G17)=0,"",TEXT(A17,"00")&amp;" · "&amp;D17&amp;" | "&amp;E17&amp;" | "&amp;F17)</f>
-        <v>01 · Prospección | Fútbol | Amplia</v>
+        <f>IF(COUNTA(A17:G17)=0,"",TEXT(A17,"00")&amp;"_"&amp;UPPER(D17)&amp;"_"&amp;E17&amp;"_"&amp;F17)</f>
       </c>
     </row>
     <row r="18" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2509,8 +2504,7 @@
         <v>76</v>
       </c>
       <c r="H18" s="6" t="str">
-        <f>IF(COUNTA(A18:G18)=0,"",TEXT(A18,"00")&amp;" · "&amp;D18&amp;" | "&amp;E18&amp;" | "&amp;F18)</f>
-        <v>02 · Prospección | Apuestas deportivas | Palabras clave</v>
+        <f>IF(COUNTA(A18:G18)=0,"",TEXT(A18,"00")&amp;"_"&amp;UPPER(D18)&amp;"_"&amp;E18&amp;"_"&amp;F18)</f>
       </c>
     </row>
     <row r="19" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2536,8 +2530,7 @@
         <v>76</v>
       </c>
       <c r="H19" s="6" t="str">
-        <f>IF(COUNTA(A19:G19)=0,"",TEXT(A19,"00")&amp;" · "&amp;D19&amp;" | "&amp;E19&amp;" | "&amp;F19)</f>
-        <v>03 · CRM | Jugadores inactivos | 30 días</v>
+        <f>IF(COUNTA(A19:G19)=0,"",TEXT(A19,"00")&amp;"_"&amp;UPPER(D19)&amp;"_"&amp;E19&amp;"_"&amp;F19)</f>
       </c>
     </row>
     <row r="20" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2563,8 +2556,7 @@
         <v>76</v>
       </c>
       <c r="H20" s="6" t="str">
-        <f>IF(COUNTA(A20:G20)=0,"",TEXT(A20,"00")&amp;" · "&amp;D20&amp;" | "&amp;E20&amp;" | "&amp;F20)</f>
-        <v>04 · Remarketing | Video viewers | 30 días</v>
+        <f>IF(COUNTA(A20:G20)=0,"",TEXT(A20,"00")&amp;"_"&amp;UPPER(D20)&amp;"_"&amp;E20&amp;"_"&amp;F20)</f>
       </c>
     </row>
     <row r="21" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2576,7 +2568,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="6" t="str">
-        <f>IF(COUNTA(A21:G21)=0,"",TEXT(A21,"00")&amp;" · "&amp;D21&amp;" | "&amp;E21&amp;" | "&amp;F21)</f>
+        <f>IF(COUNTA(A21:G21)=0,"",TEXT(A21,"00")&amp;"_"&amp;UPPER(D21)&amp;"_"&amp;E21&amp;"_"&amp;F21)</f>
         <v/>
       </c>
     </row>
@@ -2651,8 +2643,7 @@
         <v>95</v>
       </c>
       <c r="H25" s="6" t="str">
-        <f>IF(COUNTA(A25:G25)=0,"",TEXT(A25,"00")&amp;" · "&amp;D25&amp;" | "&amp;E25&amp;" | "&amp;F25&amp;" | "&amp;G25)</f>
-        <v>01 · Video | Bono de bienvenida | Regístrate | V01</v>
+        <f>IF(COUNTA(A25:G25)=0,"",TEXT(A25,"00")&amp;"_"&amp;UPPER(D25)&amp;"_"&amp;E25&amp;"_"&amp;F25&amp;"_"&amp;G25)</f>
       </c>
     </row>
     <row r="26" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2678,8 +2669,7 @@
         <v>95</v>
       </c>
       <c r="H26" s="6" t="str">
-        <f>IF(COUNTA(A26:G26)=0,"",TEXT(A26,"00")&amp;" · "&amp;D26&amp;" | "&amp;E26&amp;" | "&amp;F26&amp;" | "&amp;G26)</f>
-        <v>02 · Responsive Search Ad | Apuesta en vivo | Juega ahora | V01</v>
+        <f>IF(COUNTA(A26:G26)=0,"",TEXT(A26,"00")&amp;"_"&amp;UPPER(D26)&amp;"_"&amp;E26&amp;"_"&amp;F26&amp;"_"&amp;G26)</f>
       </c>
     </row>
     <row r="27" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2705,8 +2695,7 @@
         <v>95</v>
       </c>
       <c r="H27" s="6" t="str">
-        <f>IF(COUNTA(A27:G27)=0,"",TEXT(A27,"00")&amp;" · "&amp;D27&amp;" | "&amp;E27&amp;" | "&amp;F27&amp;" | "&amp;G27)</f>
-        <v>03 · Estático | Bono de recarga | Recarga | V01</v>
+        <f>IF(COUNTA(A27:G27)=0,"",TEXT(A27,"00")&amp;"_"&amp;UPPER(D27)&amp;"_"&amp;E27&amp;"_"&amp;F27&amp;"_"&amp;G27)</f>
       </c>
     </row>
     <row r="28" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2732,8 +2721,7 @@
         <v>107</v>
       </c>
       <c r="H28" s="6" t="str">
-        <f>IF(COUNTA(A28:G28)=0,"",TEXT(A28,"00")&amp;" · "&amp;D28&amp;" | "&amp;E28&amp;" | "&amp;F28&amp;" | "&amp;G28)</f>
-        <v>04 · Video | Pronóstico del partido | Apuesta ahora | V02</v>
+        <f>IF(COUNTA(A28:G28)=0,"",TEXT(A28,"00")&amp;"_"&amp;UPPER(D28)&amp;"_"&amp;E28&amp;"_"&amp;F28&amp;"_"&amp;G28)</f>
       </c>
     </row>
     <row r="29" spans="1:8" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2745,7 +2733,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="6" t="str">
-        <f>IF(COUNTA(A29:G29)=0,"",TEXT(A29,"00")&amp;" · "&amp;D29&amp;" | "&amp;E29&amp;" | "&amp;F29&amp;" | "&amp;G29)</f>
+        <f>IF(COUNTA(A29:G29)=0,"",TEXT(A29,"00")&amp;"_"&amp;UPPER(D29)&amp;"_"&amp;E29&amp;"_"&amp;F29&amp;"_"&amp;G29)</f>
         <v/>
       </c>
     </row>
